--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/o-higgins.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3944-198-CM25</t>
+          <t>889473-1484-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8565.540000000001</v>
+        <v>14768.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>889473-1484-CM25</t>
+          <t>3944-198-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,17 +961,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.091.500-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>14768.11</v>
+        <v>8565.540000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>598-318-CM25</t>
+          <t>1529-403-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>12495.33</v>
+        <v>7909.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1529-403-CM25</t>
+          <t>1469101-5-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7909.87</v>
+        <v>14780.37</v>
       </c>
     </row>
     <row r="14">
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1469101-5-CM25</t>
+          <t>594965-216-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA  </t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>14780.37</v>
+        <v>5780.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>594965-216-CM25</t>
+          <t>591-7694-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IGMA CONSULTORES LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.465.697-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5780.68</v>
+        <v>44533.16</v>
       </c>
     </row>
     <row r="17">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3948-66-CM26</t>
+          <t>1375760-2-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.073.800-7</t>
+          <t>61.981.310-3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NAVIDAD</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>16671.56</v>
+        <v>19027.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3863-118-CM26</t>
+          <t>3948-66-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.073.800-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE NAVIDAD</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>7347.86</v>
+        <v>16671.56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2675-128-CM26</t>
+          <t>3863-118-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>11.216.890-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>30430.67</v>
+        <v>7347.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3500-135-CM26</t>
+          <t>2675-128-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.081.700-4</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>11507.69</v>
+        <v>30430.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3982-273-CM26</t>
+          <t>3500-135-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>69.081.700-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,6 +1789,67 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
+        <v>11507.69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3982-273-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.090.900-6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
         <v>50822.44</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/o-higgins.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/o-higgins.xlsx
@@ -623,7 +623,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1781,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1846,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1911,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/o-higgins.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/o-higgins.xlsx
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
